--- a/output/pdf_financials_xlsx/XTC.xlsx
+++ b/output/pdf_financials_xlsx/XTC.xlsx
@@ -44202,7 +44202,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -48461,7 +48461,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">

--- a/output/pdf_financials_xlsx/XTC.xlsx
+++ b/output/pdf_financials_xlsx/XTC.xlsx
@@ -7195,28 +7195,28 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>3.267</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.254</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.534</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.587</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>1.066</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>3.135</v>
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
@@ -7224,22 +7224,22 @@
         </is>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>1.386</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.381</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>1.192</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="113">
@@ -30474,7 +30474,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
